--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:39:17+00:00</t>
+    <t>2026-08-28T13:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:49:20+00:00</t>
+    <t>2026-08-28T14:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:00:29+00:00</t>
+    <t>2026-08-31T13:41:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3414" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3414" uniqueCount="560">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:41:24+00:00</t>
+    <t>2026-09-02T03:14:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1141,6 +1141,10 @@
   </si>
   <si>
     <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-seltene/ValueSet/mii-vs-seltene-blutgruppe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:system}
+</t>
   </si>
   <si>
     <t>Observation.value[x].coding:loinc</t>
@@ -7284,7 +7288,7 @@
         <v>82</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>243</v>
+        <v>357</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
@@ -7329,13 +7333,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>355</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>82</v>
@@ -7453,10 +7457,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7571,10 +7575,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7691,10 +7695,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7702,7 +7706,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>93</v>
@@ -7720,16 +7724,16 @@
         <v>134</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7739,7 +7743,7 @@
         <v>82</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="T47" t="s" s="2">
         <v>82</v>
@@ -7778,7 +7782,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7802,7 +7806,7 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7813,10 +7817,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7842,13 +7846,13 @@
         <v>107</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7898,7 +7902,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7922,7 +7926,7 @@
         <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7933,10 +7937,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7962,14 +7966,14 @@
         <v>168</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8018,7 +8022,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8042,7 +8046,7 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8053,10 +8057,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8082,14 +8086,14 @@
         <v>107</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8138,7 +8142,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8162,7 +8166,7 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8173,10 +8177,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8199,19 +8203,19 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8260,7 +8264,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8284,7 +8288,7 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8295,13 +8299,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>355</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>82</v>
@@ -8419,10 +8423,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8537,10 +8541,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8657,10 +8661,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8668,7 +8672,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>93</v>
@@ -8686,16 +8690,16 @@
         <v>134</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8705,7 +8709,7 @@
         <v>82</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>82</v>
@@ -8744,7 +8748,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8768,7 +8772,7 @@
         <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8779,10 +8783,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8808,13 +8812,13 @@
         <v>107</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8864,7 +8868,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8888,7 +8892,7 @@
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8899,10 +8903,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8928,14 +8932,14 @@
         <v>168</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8984,7 +8988,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9008,7 +9012,7 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9019,10 +9023,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9048,14 +9052,14 @@
         <v>107</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9104,7 +9108,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9128,7 +9132,7 @@
         <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9139,10 +9143,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9165,19 +9169,19 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9226,7 +9230,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9250,7 +9254,7 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9261,10 +9265,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9383,10 +9387,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9412,16 +9416,16 @@
         <v>236</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9449,10 +9453,10 @@
         <v>150</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9470,7 +9474,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9479,7 +9483,7 @@
         <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>105</v>
@@ -9494,7 +9498,7 @@
         <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9505,14 +9509,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9534,16 +9538,16 @@
         <v>236</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9571,10 +9575,10 @@
         <v>150</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9592,7 +9596,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9613,24 +9617,24 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9653,19 +9657,19 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9714,7 +9718,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9738,7 +9742,7 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9749,10 +9753,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9778,13 +9782,13 @@
         <v>236</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9813,10 +9817,10 @@
         <v>158</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9834,7 +9838,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9855,24 +9859,24 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9898,16 +9902,16 @@
         <v>236</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -9935,10 +9939,10 @@
         <v>158</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
@@ -9956,7 +9960,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9980,7 +9984,7 @@
         <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -9991,10 +9995,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10017,16 +10021,16 @@
         <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10076,7 +10080,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10097,24 +10101,24 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10137,16 +10141,16 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10196,7 +10200,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10217,24 +10221,24 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10257,19 +10261,19 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10318,7 +10322,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10330,7 +10334,7 @@
         <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
@@ -10342,7 +10346,7 @@
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10353,10 +10357,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10471,10 +10475,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10591,14 +10595,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10620,10 +10624,10 @@
         <v>113</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N71" t="s" s="2">
         <v>116</v>
@@ -10678,7 +10682,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10713,10 +10717,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10739,13 +10743,13 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10796,7 +10800,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10805,7 +10809,7 @@
         <v>93</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>105</v>
@@ -10820,7 +10824,7 @@
         <v>82</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -10831,10 +10835,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10857,13 +10861,13 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10914,7 +10918,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10923,7 +10927,7 @@
         <v>93</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>105</v>
@@ -10938,7 +10942,7 @@
         <v>82</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -10949,10 +10953,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10978,16 +10982,16 @@
         <v>236</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -11015,10 +11019,10 @@
         <v>172</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>82</v>
@@ -11036,7 +11040,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11057,10 +11061,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11071,10 +11075,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11100,16 +11104,16 @@
         <v>236</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11137,10 +11141,10 @@
         <v>158</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>82</v>
@@ -11158,7 +11162,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11179,10 +11183,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11193,10 +11197,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11219,17 +11223,17 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11278,7 +11282,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11313,10 +11317,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11342,10 +11346,10 @@
         <v>107</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11396,7 +11400,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11420,7 +11424,7 @@
         <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11431,10 +11435,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11457,16 +11461,16 @@
         <v>94</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11516,7 +11520,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11540,7 +11544,7 @@
         <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11551,10 +11555,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11577,16 +11581,16 @@
         <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11636,7 +11640,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11660,7 +11664,7 @@
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11671,10 +11675,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11697,19 +11701,19 @@
         <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -11758,7 +11762,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11782,7 +11786,7 @@
         <v>82</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -11793,10 +11797,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11911,10 +11915,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12031,14 +12035,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12060,10 +12064,10 @@
         <v>113</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>116</v>
@@ -12118,7 +12122,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12153,10 +12157,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12182,13 +12186,13 @@
         <v>236</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O84" t="s" s="2">
         <v>253</v>
@@ -12240,7 +12244,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>93</v>
@@ -12261,7 +12265,7 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>259</v>
@@ -12275,10 +12279,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12301,16 +12305,16 @@
         <v>94</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M85" t="s" s="2">
         <v>346</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O85" t="s" s="2">
         <v>348</v>
@@ -12362,7 +12366,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12383,7 +12387,7 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>351</v>
@@ -12397,10 +12401,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12426,16 +12430,16 @@
         <v>236</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12463,10 +12467,10 @@
         <v>150</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>82</v>
@@ -12484,7 +12488,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12493,7 +12497,7 @@
         <v>93</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>105</v>
@@ -12508,7 +12512,7 @@
         <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12519,14 +12523,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12548,16 +12552,16 @@
         <v>236</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12585,10 +12589,10 @@
         <v>150</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>82</v>
@@ -12606,7 +12610,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12627,24 +12631,24 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12670,16 +12674,16 @@
         <v>83</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -12728,7 +12732,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12752,7 +12756,7 @@
         <v>82</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:14:53+00:00</t>
+    <t>2026-09-02T03:38:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:38:58+00:00</t>
+    <t>2026-09-02T04:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T04:00:55+00:00</t>
+    <t>2026-09-02T06:41:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:41:45+00:00</t>
+    <t>2026-09-02T06:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:59:28+00:00</t>
+    <t>2026-09-02T09:29:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:29:03+00:00</t>
+    <t>2026-09-02T14:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -285,7 +285,7 @@
 dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
-    <t>Messbefunde.Blutgruppe</t>
+    <t>Messbefunde.blutgruppe</t>
   </si>
   <si>
     <t>Event</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:14:40+00:00</t>
+    <t>2026-09-02T14:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -285,7 +285,7 @@
 dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
-    <t>Messbefunde.blutgruppe</t>
+    <t>koerperlicheUntersuchung.blutgruppe</t>
   </si>
   <si>
     <t>Event</t>
@@ -938,7 +938,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>Patient</t>
+    <t>persoenlicheInfosIndexpatient</t>
   </si>
   <si>
     <t>Event.subject</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:33:43+00:00</t>
+    <t>2026-09-02T15:16:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:16:54+00:00</t>
+    <t>2026-09-02T16:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:13:05+00:00</t>
+    <t>2026-09-02T16:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:35:11+00:00</t>
+    <t>2026-09-02T16:52:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:52:58+00:00</t>
+    <t>2026-09-02T17:07:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:07:58+00:00</t>
+    <t>2026-09-02T17:34:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:34:23+00:00</t>
+    <t>2026-09-02T17:52:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:52:03+00:00</t>
+    <t>2026-09-02T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T18:22:51+00:00</t>
+    <t>2026-09-03T06:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T06:59:35+00:00</t>
+    <t>2026-09-03T07:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:17:59+00:00</t>
+    <t>2026-09-03T07:33:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:33:22+00:00</t>
+    <t>2026-09-03T09:08:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:08:22+00:00</t>
+    <t>2026-09-03T09:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:27:13+00:00</t>
+    <t>2026-09-03T09:44:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-blutgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:44:41+00:00</t>
+    <t>2026-09-03T10:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
